--- a/builder-eo/src/main/resources/eo.xlsx
+++ b/builder-eo/src/main/resources/eo.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/werner.diwischek/dev/elasticobjects/builder-eo/src/main/resources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{184A566F-D201-1043-9D08-A9D868C4078A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAFD320-459E-F344-A375-33D4193C82DA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="560" yWindow="480" windowWidth="28240" windowHeight="17540" xr2:uid="{1E8B47EF-5738-BE4A-AAD2-1678499A82C4}"/>
+    <workbookView xWindow="1240" yWindow="1120" windowWidth="28240" windowHeight="17540" activeTab="2" xr2:uid="{1E8B47EF-5738-BE4A-AAD2-1678499A82C4}"/>
   </bookViews>
   <sheets>
     <sheet name="ModelConfig" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DbSqlConfig!$A$1:$I$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">FieldConfig!$A$1:$J$169</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">FileConfig!$A$1:$N$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ModelConfig!$A$1:$N$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ModelConfig!$A$1:$N$165</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <fileRecoveryPr repairLoad="1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3478" uniqueCount="938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3489" uniqueCount="937">
   <si>
     <t>naturalId</t>
   </si>
@@ -2196,9 +2196,6 @@
     <t>A bean container class for Model values</t>
   </si>
   <si>
-    <t>[   "module","moduleScope","fileEnding", "targetFileConfigKey"]</t>
-  </si>
-  <si>
     <t>classes.java</t>
   </si>
   <si>
@@ -2241,12 +2238,6 @@
     <t>Abstract super class for generating code based on ModelBeans.json.</t>
   </si>
   <si>
-    <t>GenerateModelProperties</t>
-  </si>
-  <si>
-    <t>GenerateProperties</t>
-  </si>
-  <si>
     <t xml:space="preserve">Instance abstract base class for generating code with targetFileConfigKey and filter module, moduleScope values. </t>
   </si>
   <si>
@@ -2278,9 +2269,6 @@
   </si>
   <si>
     <t>override</t>
-  </si>
-  <si>
-    <t>[   "module","moduleScope","fileEnding", "targetFileConfigKey", "projectDirectory", "sourceFileConfigKey"]</t>
   </si>
   <si>
     <t>ParamsEoConfigs.json</t>
@@ -3057,6 +3045,15 @@
   </si>
   <si>
     <t>CsvConfigInterface,ListProperties</t>
+  </si>
+  <si>
+    <t>GenerateModelInterface</t>
+  </si>
+  <si>
+    <t>GenerateAbstractInterface</t>
+  </si>
+  <si>
+    <t>module, moduleScope, fileEnding, targetFileConfigKey, projectDirectory, sourceFileConfigKey</t>
   </si>
 </sst>
 </file>
@@ -3446,7 +3443,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E2949A4-7E1C-7F4B-A1BC-11445B521B01}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:S164"/>
+  <dimension ref="A1:S165"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="17.83203125" style="2" customWidth="1"/>
@@ -3529,7 +3526,7 @@
         <v>35</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>147</v>
@@ -3538,7 +3535,7 @@
         <v>146</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="N2" s="2" t="s">
         <v>148</v>
@@ -3564,7 +3561,7 @@
         <v>14</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>484</v>
@@ -3573,7 +3570,7 @@
         <v>417</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N3" s="2" t="s">
         <v>148</v>
@@ -3605,7 +3602,7 @@
         <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="177" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
@@ -3631,7 +3628,7 @@
         <v>150</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>151</v>
@@ -3651,7 +3648,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>14</v>
@@ -3666,7 +3663,7 @@
         <v>418</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>148</v>
@@ -3680,7 +3677,7 @@
     </row>
     <row r="7" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>10</v>
@@ -3689,16 +3686,16 @@
         <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>483</v>
@@ -3708,13 +3705,13 @@
         <v>BaseBean</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>148</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="P7" s="6">
         <v>42725</v>
@@ -3722,7 +3719,7 @@
     </row>
     <row r="8" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>10</v>
@@ -3731,10 +3728,10 @@
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>35</v>
@@ -3750,13 +3747,13 @@
         <v>BaseBeanInterface</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>148</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="P8" s="6">
         <v>44186</v>
@@ -3764,7 +3761,7 @@
     </row>
     <row r="9" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>10</v>
@@ -3773,16 +3770,16 @@
         <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>483</v>
@@ -3792,13 +3789,13 @@
         <v>BaseConfig</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>148</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="P9" s="6">
         <v>44186</v>
@@ -3806,7 +3803,7 @@
     </row>
     <row r="10" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>10</v>
@@ -3815,7 +3812,7 @@
         <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>35</v>
@@ -3831,13 +3828,13 @@
         <v>BaseConfigInterface</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>148</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="P10" s="6">
         <v>44186</v>
@@ -3860,7 +3857,7 @@
         <v>35</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>152</v>
@@ -3869,7 +3866,7 @@
         <v>16</v>
       </c>
       <c r="M11" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>151</v>
@@ -3901,7 +3898,7 @@
         <v>153</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>148</v>
@@ -3937,7 +3934,7 @@
         <v>CallContent</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>148</v>
@@ -3957,19 +3954,19 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>153</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>154</v>
@@ -3979,7 +3976,7 @@
         <v>CallImpl</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>148</v>
@@ -4012,7 +4009,7 @@
         <v>Class</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>151</v>
@@ -4042,7 +4039,7 @@
         <v>Condition</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N16" s="2" t="s">
         <v>148</v>
@@ -4081,7 +4078,7 @@
         <v>ConfigAsFlatListCall</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N17" s="2" t="s">
         <v>148</v>
@@ -4098,19 +4095,19 @@
         <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>160</v>
@@ -4120,7 +4117,7 @@
         <v>ConfigBean</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>148</v>
@@ -4131,7 +4128,7 @@
     </row>
     <row r="19" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>10</v>
@@ -4140,10 +4137,10 @@
         <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>872</v>
+        <v>868</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>35</v>
@@ -4159,7 +4156,7 @@
         <v>ConfigBeanInterface</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>148</v>
@@ -4201,7 +4198,7 @@
         <v>ConfigCall</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>148</v>
@@ -4212,7 +4209,7 @@
     </row>
     <row r="21" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>10</v>
@@ -4221,13 +4218,13 @@
         <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>35</v>
@@ -4243,7 +4240,7 @@
         <v>ConfigConfig</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>148</v>
@@ -4254,7 +4251,7 @@
     </row>
     <row r="22" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>10</v>
@@ -4263,10 +4260,10 @@
         <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>35</v>
@@ -4282,7 +4279,7 @@
         <v>ConfigConfigInterface</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>148</v>
@@ -4318,7 +4315,7 @@
         <v>ConfigDirectoryReadCommand</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N23" s="2" t="s">
         <v>148</v>
@@ -4357,7 +4354,7 @@
         <v>ConfigKeysCall</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>148</v>
@@ -4393,7 +4390,7 @@
         <v>ConfigLinkCall</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N25" s="2" t="s">
         <v>148</v>
@@ -4434,7 +4431,7 @@
         <v>167</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>148</v>
@@ -4470,7 +4467,7 @@
         <v>ConfigReadCommand</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>148</v>
@@ -4506,7 +4503,7 @@
         <v>ConfigReadWriteCommand</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>148</v>
@@ -4539,7 +4536,7 @@
         <v>ConfigsCommand</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>148</v>
@@ -4574,7 +4571,7 @@
         <v>171</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>148</v>
@@ -4610,13 +4607,13 @@
         <v>ConfigWriteCommand</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="51" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>370</v>
       </c>
@@ -4627,7 +4624,7 @@
         <v>11</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>178</v>
@@ -4645,7 +4642,7 @@
         <v>370</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>148</v>
@@ -4653,7 +4650,7 @@
     </row>
     <row r="33" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>10</v>
@@ -4662,7 +4659,7 @@
         <v>11</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>35</v>
@@ -4678,7 +4675,7 @@
         <v>CsvConfigInterface</v>
       </c>
       <c r="M33" s="5" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>148</v>
@@ -4710,7 +4707,7 @@
         <v>371</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>148</v>
@@ -4730,7 +4727,7 @@
         <v>11</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>798</v>
+        <v>794</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>335</v>
@@ -4752,7 +4749,7 @@
         <v>CsvSimpleReadCall</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>148</v>
@@ -4791,7 +4788,7 @@
         <v>CsvSimpleWriteCall</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>148</v>
@@ -4826,7 +4823,7 @@
         <v>374</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>148</v>
@@ -4858,12 +4855,12 @@
         <v>30</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="39" spans="1:19" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>241</v>
@@ -4872,19 +4869,19 @@
         <v>11</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="K39" s="2" t="s">
         <v>154</v>
@@ -4894,7 +4891,7 @@
         <v>DbBean</v>
       </c>
       <c r="M39" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N39" s="2" t="s">
         <v>148</v>
@@ -4902,7 +4899,7 @@
     </row>
     <row r="40" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>241</v>
@@ -4911,7 +4908,7 @@
         <v>11</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>35</v>
@@ -4927,7 +4924,7 @@
         <v>DbBeanInterface</v>
       </c>
       <c r="M40" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N40" s="2" t="s">
         <v>148</v>
@@ -4944,10 +4941,10 @@
         <v>11</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>802</v>
+        <v>798</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>182</v>
@@ -4956,7 +4953,7 @@
         <v>35</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>154</v>
@@ -4966,7 +4963,7 @@
         <v>DbConfig</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>148</v>
@@ -4974,7 +4971,7 @@
     </row>
     <row r="42" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>241</v>
@@ -4983,7 +4980,7 @@
         <v>11</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>35</v>
@@ -4999,7 +4996,7 @@
         <v>DbConfigInterface</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>148</v>
@@ -5035,7 +5032,7 @@
         <v>DbModelCall</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>148</v>
@@ -5074,7 +5071,7 @@
         <v>DbModelDeleteCall</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>148</v>
@@ -5113,7 +5110,7 @@
         <v>DbModelReadCall</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>148</v>
@@ -5152,7 +5149,7 @@
         <v>DbModelWriteCall</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>148</v>
@@ -5163,7 +5160,7 @@
     </row>
     <row r="47" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>808</v>
+        <v>804</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>241</v>
@@ -5172,13 +5169,13 @@
         <v>11</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>35</v>
@@ -5194,7 +5191,7 @@
         <v>DbSqlBean</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>148</v>
@@ -5205,7 +5202,7 @@
     </row>
     <row r="48" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>241</v>
@@ -5214,16 +5211,16 @@
         <v>11</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>242</v>
@@ -5233,7 +5230,7 @@
         <v>DbSqlBeanInterface</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>148</v>
@@ -5269,7 +5266,7 @@
         <v>DbSqlCall</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>148</v>
@@ -5286,19 +5283,19 @@
         <v>11</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>242</v>
@@ -5308,7 +5305,7 @@
         <v>DbSqlConfig</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N50" s="2" t="s">
         <v>148</v>
@@ -5319,7 +5316,7 @@
     </row>
     <row r="51" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>241</v>
@@ -5328,16 +5325,16 @@
         <v>11</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>242</v>
@@ -5347,7 +5344,7 @@
         <v>DbSqlConfigInterface</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="N51" s="2" t="s">
         <v>148</v>
@@ -5383,7 +5380,7 @@
         <v>DbSqlExecuteCall</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>148</v>
@@ -5419,7 +5416,7 @@
         <v>DbSqlReadCall</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>148</v>
@@ -5455,7 +5452,7 @@
         <v>DbTypes</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="N54" s="2" t="s">
         <v>148</v>
@@ -5488,7 +5485,7 @@
         <v>DirectoryConfig</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>148</v>
@@ -5524,7 +5521,7 @@
         <v>DirectoryListReadCall</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>148</v>
@@ -5563,7 +5560,7 @@
         <v>DirectoryMapReadCall</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>148</v>
@@ -5605,7 +5602,7 @@
         <v>DirectoryReadCall</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>148</v>
@@ -5644,7 +5641,7 @@
         <v>DirectoryWriteCall</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>148</v>
@@ -5676,7 +5673,7 @@
         <v>131</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
@@ -5705,7 +5702,7 @@
         <v>172</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>148</v>
@@ -5734,7 +5731,7 @@
         <v>174</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="N62" s="2" t="s">
         <v>148</v>
@@ -5766,7 +5763,7 @@
         <v>45</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>148</v>
@@ -5783,10 +5780,10 @@
         <v>11</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>694</v>
@@ -5795,7 +5792,7 @@
         <v>35</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
       <c r="K64" s="2" t="s">
         <v>160</v>
@@ -5805,7 +5802,7 @@
         <v>FieldBean</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="N64" s="2" t="s">
         <v>148</v>
@@ -5814,9 +5811,9 @@
         <v>44174</v>
       </c>
     </row>
-    <row r="65" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>301</v>
@@ -5825,7 +5822,7 @@
         <v>11</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>692</v>
@@ -5844,7 +5841,7 @@
         <v>FieldBeanGen</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>148</v>
@@ -5855,7 +5852,7 @@
     </row>
     <row r="66" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>10</v>
@@ -5864,16 +5861,16 @@
         <v>11</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J66" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>160</v>
@@ -5883,7 +5880,7 @@
         <v>FieldBeanInterface</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="N66" s="2" t="s">
         <v>148</v>
@@ -5895,9 +5892,9 @@
         <v>44145</v>
       </c>
     </row>
-    <row r="67" spans="1:19" ht="372" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:19" ht="372" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>301</v>
@@ -5906,16 +5903,16 @@
         <v>11</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="K67" s="2" t="s">
         <v>160</v>
@@ -5925,15 +5922,15 @@
         <v>FieldBeanInterface4Java</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N67" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="68" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>301</v>
@@ -5942,13 +5939,13 @@
         <v>11</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>160</v>
@@ -5958,7 +5955,7 @@
         <v>FieldBeanInterface4Javascript</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>148</v>
@@ -5975,19 +5972,19 @@
         <v>11</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>160</v>
@@ -5996,7 +5993,7 @@
         <v>177</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="N69" s="2" t="s">
         <v>148</v>
@@ -6007,7 +6004,7 @@
     </row>
     <row r="70" spans="1:19" ht="102" hidden="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>10</v>
@@ -6016,16 +6013,16 @@
         <v>11</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>160</v>
@@ -6035,7 +6032,7 @@
         <v>FieldConfigInterface</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>148</v>
@@ -6049,7 +6046,7 @@
     </row>
     <row r="71" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>10</v>
@@ -6058,19 +6055,19 @@
         <v>11</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="K71" s="2" t="s">
         <v>179</v>
@@ -6080,7 +6077,7 @@
         <v>FileBean</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="N71" s="2" t="s">
         <v>148</v>
@@ -6094,7 +6091,7 @@
     </row>
     <row r="72" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>10</v>
@@ -6103,10 +6100,10 @@
         <v>11</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>35</v>
@@ -6122,7 +6119,7 @@
         <v>FileBeanInterface</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>148</v>
@@ -6164,7 +6161,7 @@
         <v>FileCall</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="N73" s="2" t="s">
         <v>148</v>
@@ -6181,13 +6178,13 @@
         <v>11</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>35</v>
@@ -6202,7 +6199,7 @@
         <v>178</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>148</v>
@@ -6216,7 +6213,7 @@
     </row>
     <row r="75" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>10</v>
@@ -6225,10 +6222,10 @@
         <v>11</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>35</v>
@@ -6244,7 +6241,7 @@
         <v>FileConfigInterface</v>
       </c>
       <c r="M75" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="N75" s="2" t="s">
         <v>148</v>
@@ -6255,7 +6252,7 @@
     </row>
     <row r="76" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>10</v>
@@ -6264,7 +6261,7 @@
         <v>11</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>35</v>
@@ -6280,7 +6277,7 @@
         <v>FileConfigInterfaceMethods</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="N76" s="2" t="s">
         <v>148</v>
@@ -6321,7 +6318,7 @@
         <v>180</v>
       </c>
       <c r="M77" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N77" s="2" t="s">
         <v>148</v>
@@ -6360,7 +6357,7 @@
         <v>FileReadWriteCall</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N78" s="2" t="s">
         <v>148</v>
@@ -6380,7 +6377,7 @@
         <v>11</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>638</v>
@@ -6401,7 +6398,7 @@
         <v>181</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>148</v>
@@ -6433,15 +6430,15 @@
         <v>132</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="S80" s="7">
         <v>44108</v>
       </c>
     </row>
-    <row r="81" spans="1:19" ht="85" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>301</v>
@@ -6450,7 +6447,10 @@
         <v>11</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>725</v>
+        <v>936</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>935</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>156</v>
@@ -6459,7 +6459,7 @@
         <v>35</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>494</v>
@@ -6469,7 +6469,7 @@
         <v>GenerateAbstract</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>148</v>
@@ -6478,9 +6478,9 @@
         <v>44105</v>
       </c>
     </row>
-    <row r="82" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:19" ht="68" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
-        <v>717</v>
+        <v>935</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>301</v>
@@ -6489,35 +6489,34 @@
         <v>11</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>495</v>
+        <v>936</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>710</v>
+        <v>153</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>496</v>
+        <v>636</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>494</v>
       </c>
       <c r="L82" s="2" t="str">
         <f>A82</f>
-        <v>GenerateEoConfigJsonCall</v>
+        <v>GenerateAbstractInterface</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>864</v>
+        <v>764</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P82" s="6"/>
-    </row>
-    <row r="83" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="83" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>301</v>
@@ -6525,38 +6524,36 @@
       <c r="D83" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>712</v>
+      <c r="E83" s="2" t="s">
+        <v>495</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>711</v>
+        <v>496</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>494</v>
       </c>
       <c r="L83" s="2" t="str">
         <f>A83</f>
-        <v>GenerateModelAbstract</v>
+        <v>GenerateEoConfigJsonCall</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>923</v>
+        <v>860</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S83" s="6">
-        <v>44121</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="P83" s="6"/>
+    </row>
+    <row r="84" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>301</v>
@@ -6564,33 +6561,38 @@
       <c r="D84" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="F84" s="2" t="s">
+        <v>934</v>
+      </c>
       <c r="G84" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J84" s="2" t="s">
         <v>710</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>719</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>494</v>
       </c>
       <c r="L84" s="2" t="str">
         <f>A84</f>
-        <v>GenerateModelBeansJsonCall</v>
+        <v>GenerateModelAbstract</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>864</v>
+        <v>919</v>
       </c>
       <c r="N84" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P84" s="6"/>
-    </row>
-    <row r="85" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="S84" s="6">
+        <v>44121</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>301</v>
@@ -6598,33 +6600,36 @@
       <c r="D85" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>731</v>
+      <c r="F85" s="2" t="s">
+        <v>934</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="I85" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>732</v>
+        <v>710</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>494</v>
       </c>
       <c r="L85" s="2" t="str">
         <f>A85</f>
-        <v>GenerateModelProperties</v>
+        <v>GenerateModelAbstract</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>768</v>
+        <v>919</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="86" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="S85" s="6">
+        <v>44121</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>715</v>
       </c>
@@ -6648,18 +6653,19 @@
       </c>
       <c r="L86" s="2" t="str">
         <f>A86</f>
-        <v>GenerateModelTemplateCall</v>
+        <v>GenerateModelBeansJsonCall</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="87" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="P86" s="6"/>
+    </row>
+    <row r="87" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
-        <v>720</v>
+        <v>934</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>301</v>
@@ -6667,32 +6673,35 @@
       <c r="D87" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E87" s="2" t="s">
+        <v>727</v>
+      </c>
       <c r="G87" s="2" t="s">
-        <v>709</v>
+        <v>935</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>494</v>
       </c>
       <c r="L87" s="2" t="str">
         <f>A87</f>
-        <v>GenerateModelTemplateMapCall</v>
+        <v>GenerateModelInterface</v>
       </c>
       <c r="M87" s="2" t="s">
-        <v>864</v>
+        <v>764</v>
       </c>
       <c r="N87" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="88" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>301</v>
@@ -6700,103 +6709,107 @@
       <c r="D88" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>697</v>
-      </c>
       <c r="G88" s="2" t="s">
-        <v>153</v>
+        <v>708</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>636</v>
+        <v>713</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>494</v>
       </c>
       <c r="L88" s="2" t="str">
         <f>A88</f>
-        <v>GenerateProperties</v>
+        <v>GenerateModelTemplateCall</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>768</v>
+        <v>860</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="89" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:19" ht="51" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
-        <v>455</v>
+        <v>717</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>251</v>
+        <v>301</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="G89" s="2" t="s">
-        <v>156</v>
+        <v>708</v>
       </c>
       <c r="I89" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>457</v>
+        <v>713</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>184</v>
+        <v>494</v>
       </c>
       <c r="L89" s="2" t="str">
         <f>A89</f>
-        <v>GithubLinkCall</v>
+        <v>GenerateModelTemplateMapCall</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S89" s="7">
+    </row>
+    <row r="90" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="L90" s="2" t="str">
+        <f>A90</f>
+        <v>GithubLinkCall</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="S90" s="7">
         <v>44108</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L90" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="M90" s="2" t="s">
-        <v>857</v>
-      </c>
-      <c r="N90" s="2" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="91" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
-        <v>794</v>
+        <v>32</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>10</v>
@@ -6804,69 +6817,53 @@
       <c r="D91" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F91" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="G91" s="2" t="s">
-        <v>783</v>
-      </c>
       <c r="I91" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>779</v>
+      </c>
+      <c r="I92" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J91" s="2" t="s">
+      <c r="J92" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="L91" s="2" t="str">
-        <f>A91</f>
-        <v>HostBean</v>
-      </c>
-      <c r="M91" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="N91" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="P91" s="6">
-        <v>44181</v>
-      </c>
-      <c r="S91" s="6">
-        <v>44023</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="2" t="s">
-        <v>908</v>
-      </c>
-      <c r="F92" s="2" t="s">
-        <v>911</v>
-      </c>
-      <c r="I92" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J92" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>154</v>
       </c>
       <c r="L92" s="2" t="str">
         <f>A92</f>
-        <v>HostBeanInterface</v>
+        <v>HostBean</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>148</v>
@@ -6874,10 +6871,13 @@
       <c r="P92" s="6">
         <v>44181</v>
       </c>
+      <c r="S92" s="6">
+        <v>44023</v>
+      </c>
     </row>
     <row r="93" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
-        <v>606</v>
+        <v>903</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>10</v>
@@ -6886,37 +6886,37 @@
         <v>11</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>607</v>
+        <v>904</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G93" s="2" t="s">
-        <v>156</v>
+        <v>907</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>609</v>
+        <v>551</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>154</v>
       </c>
       <c r="L93" s="2" t="str">
         <f>A93</f>
-        <v>HostCall</v>
+        <v>HostBeanInterface</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>924</v>
+        <v>858</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="94" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="P93" s="6">
+        <v>44181</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
-        <v>182</v>
+        <v>606</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>10</v>
@@ -6924,34 +6924,38 @@
       <c r="D94" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E94" s="2" t="s">
+        <v>607</v>
+      </c>
       <c r="F94" s="2" t="s">
-        <v>787</v>
+        <v>153</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>784</v>
+        <v>156</v>
       </c>
       <c r="I94" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>183</v>
+        <v>609</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="L94" s="2" t="s">
-        <v>182</v>
+      <c r="L94" s="2" t="str">
+        <f>A94</f>
+        <v>HostCall</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="P94" s="6">
-        <v>43390</v>
+        <v>920</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="95" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
-        <v>788</v>
+        <v>182</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>10</v>
@@ -6959,38 +6963,34 @@
       <c r="D95" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>908</v>
-      </c>
       <c r="F95" s="2" t="s">
-        <v>781</v>
+        <v>783</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>780</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>551</v>
+        <v>183</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="L95" s="2" t="str">
-        <f>A95</f>
-        <v>HostConfigInterface</v>
+      <c r="L95" s="2" t="s">
+        <v>182</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>863</v>
-      </c>
-      <c r="N95" s="2" t="s">
-        <v>148</v>
+        <v>905</v>
       </c>
       <c r="P95" s="6">
-        <v>44093</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>43390</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>10</v>
@@ -6998,8 +6998,11 @@
       <c r="D96" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E96" s="2" t="s">
+        <v>904</v>
+      </c>
       <c r="F96" s="2" t="s">
-        <v>788</v>
+        <v>777</v>
       </c>
       <c r="I96" s="2" t="s">
         <v>35</v>
@@ -7012,47 +7015,57 @@
       </c>
       <c r="L96" s="2" t="str">
         <f>A96</f>
-        <v>HostConfigInterfaceMethods</v>
+        <v>HostConfigInterface</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="N96" s="2" t="s">
         <v>148</v>
       </c>
       <c r="P96" s="6">
+        <v>44093</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L97" s="2" t="str">
+        <f>A97</f>
+        <v>HostConfigInterfaceMethods</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="P97" s="6">
         <v>44181</v>
       </c>
     </row>
-    <row r="97" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="2" t="s">
+    <row r="98" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L97" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="M97" s="2" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="98" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>207</v>
@@ -7067,86 +7080,83 @@
         <v>35</v>
       </c>
       <c r="K98" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K99" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="L98" s="2" t="s">
+      <c r="L99" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="M98" s="2" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="2" t="s">
+      <c r="M99" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="C99" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="2" t="s">
+      <c r="C100" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="G99" s="2" t="s">
+      <c r="G100" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="I99" s="2" t="s">
+      <c r="I100" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J99" s="2" t="s">
+      <c r="J100" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="K99" s="2" t="s">
+      <c r="K100" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="L99" s="2" t="str">
-        <f>A99</f>
+      <c r="L100" s="2" t="str">
+        <f>A100</f>
         <v>JsonWriteCall</v>
       </c>
-      <c r="M99" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="N99" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K100" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="L100" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="M100" s="2" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="N100" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="101" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
-        <v>188</v>
+        <v>78</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>10</v>
@@ -7154,66 +7164,66 @@
       <c r="D101" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="I101" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="L101" s="2" t="s">
-        <v>188</v>
+        <v>78</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="N101" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="102" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:16" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="L102" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="M102" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="N102" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="B102" s="2" t="s">
+      <c r="B103" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C102" s="2" t="s">
+      <c r="C103" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="L102" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="M102" s="2" t="s">
-        <v>858</v>
-      </c>
-      <c r="N102" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="103" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>11</v>
@@ -7225,24 +7235,24 @@
         <v>149</v>
       </c>
       <c r="L103" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="104" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>333</v>
+        <v>10</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>11</v>
@@ -7254,82 +7264,79 @@
         <v>149</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="N104" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="105" spans="1:14" ht="238" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="L105" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="M105" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="N105" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" ht="238" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="C105" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D105" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="2" t="s">
-        <v>789</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J105" s="2" t="s">
+      <c r="C106" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>785</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J106" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="L105" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="M105" s="5" t="s">
-        <v>768</v>
-      </c>
-      <c r="N105" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="106" spans="1:14" ht="136" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>797</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>193</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="M106" s="2" t="s">
-        <v>864</v>
+        <v>335</v>
+      </c>
+      <c r="M106" s="5" t="s">
+        <v>764</v>
       </c>
       <c r="N106" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="107" spans="1:14" ht="136" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
-        <v>573</v>
+        <v>83</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>10</v>
@@ -7338,59 +7345,65 @@
         <v>11</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="I107" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>574</v>
+        <v>194</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="L107" s="2" t="str">
-        <f>A107</f>
-        <v>ListProperties</v>
-      </c>
-      <c r="M107" s="5" t="s">
-        <v>768</v>
+      <c r="L107" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>860</v>
       </c>
       <c r="N107" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="108" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:16" ht="136" hidden="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="L108" s="2" t="str">
+        <f>A108</f>
+        <v>ListProperties</v>
+      </c>
+      <c r="M108" s="5" t="s">
+        <v>764</v>
+      </c>
+      <c r="N108" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="B108" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="L108" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="M108" s="2" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="109" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="B109" s="5" t="s">
+      <c r="B109" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C109" s="2" t="s">
@@ -7403,18 +7416,21 @@
         <v>35</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>152</v>
+        <v>185</v>
       </c>
       <c r="L109" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M109" s="2" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="110" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="2" t="s">
-        <v>195</v>
+      <c r="B110" s="5" t="s">
+        <v>207</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>333</v>
@@ -7426,54 +7442,41 @@
         <v>35</v>
       </c>
       <c r="K110" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="L110" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K111" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="L110" s="2" t="s">
+      <c r="L111" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="M110" s="2" t="s">
-        <v>858</v>
-      </c>
-    </row>
-    <row r="111" spans="1:14" ht="404" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>801</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>836</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="L111" s="2" t="str">
-        <f>A111</f>
-        <v>Model</v>
-      </c>
       <c r="M111" s="2" t="s">
-        <v>813</v>
-      </c>
-      <c r="N111" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="112" spans="1:14" ht="119" hidden="1" x14ac:dyDescent="0.2">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" ht="404" hidden="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
-        <v>695</v>
+        <v>750</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>10</v>
@@ -7482,52 +7485,49 @@
         <v>11</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>755</v>
+        <v>797</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="G112" s="2" t="s">
-        <v>694</v>
+        <v>871</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>696</v>
+        <v>832</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L112" s="2" t="str">
         <f>A112</f>
-        <v>ModelBean</v>
+        <v>Model</v>
       </c>
       <c r="M112" s="2" t="s">
-        <v>864</v>
+        <v>809</v>
       </c>
       <c r="N112" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:14" ht="136" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" ht="119" hidden="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
-        <v>766</v>
+        <v>695</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>301</v>
+        <v>10</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>830</v>
+        <v>751</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>821</v>
+        <v>750</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>14</v>
@@ -7540,18 +7540,18 @@
       </c>
       <c r="L113" s="2" t="str">
         <f>A113</f>
-        <v>ModelBeanGen</v>
+        <v>ModelBean</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>913</v>
+        <v>860</v>
       </c>
       <c r="N113" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="114" spans="1:14" ht="409.6" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" ht="136" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
-        <v>821</v>
+        <v>762</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>301</v>
@@ -7560,72 +7560,73 @@
         <v>11</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>933</v>
+        <v>826</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>754</v>
+        <v>817</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>695</v>
       </c>
       <c r="I114" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J114" s="2" t="s">
-        <v>767</v>
+        <v>696</v>
       </c>
       <c r="K114" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L114" s="2" t="str">
         <f>A114</f>
-        <v>ModelBeanInterface4Java</v>
+        <v>ModelBeanGen</v>
       </c>
       <c r="M114" s="2" t="s">
-        <v>768</v>
+        <v>909</v>
       </c>
       <c r="N114" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="115" spans="1:14" ht="238" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
-        <v>197</v>
+        <v>817</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>10</v>
+        <v>301</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>824</v>
+        <v>929</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>741</v>
+        <v>750</v>
       </c>
       <c r="I115" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J115" s="2" t="s">
-        <v>198</v>
+        <v>763</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="L115" s="2" t="s">
-        <v>197</v>
+      <c r="L115" s="2" t="str">
+        <f>A115</f>
+        <v>ModelBeanInterface4Java</v>
       </c>
       <c r="M115" s="2" t="s">
-        <v>922</v>
+        <v>764</v>
       </c>
       <c r="N115" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" ht="238" hidden="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>578</v>
+        <v>197</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>10</v>
@@ -7634,109 +7635,111 @@
         <v>11</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>791</v>
+        <v>820</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>786</v>
+        <v>749</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>205</v>
+        <v>737</v>
       </c>
       <c r="I116" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J116" s="2" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="L116" s="2" t="str">
-        <f>A116</f>
-        <v>ModelConfigDbObject</v>
+      <c r="L116" s="2" t="s">
+        <v>197</v>
       </c>
       <c r="M116" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N116" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="117" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>799</v>
+        <v>10</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>580</v>
+        <v>787</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>482</v>
+        <v>205</v>
       </c>
       <c r="I117" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J117" s="2" t="s">
-        <v>552</v>
+        <v>206</v>
       </c>
       <c r="K117" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L117" s="2" t="str">
         <f>A117</f>
-        <v>ModelConfigDbProperties</v>
+        <v>ModelConfigDbObject</v>
       </c>
       <c r="M117" s="2" t="s">
-        <v>768</v>
+        <v>918</v>
       </c>
       <c r="N117" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="118" spans="1:14" ht="340" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="G118" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="C118" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>781</v>
-      </c>
       <c r="I118" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J118" s="2" t="s">
-        <v>800</v>
+        <v>552</v>
       </c>
       <c r="K118" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L118" s="2" t="str">
         <f>A118</f>
-        <v>ModelConfigInterface</v>
+        <v>ModelConfigDbProperties</v>
       </c>
       <c r="M118" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N118" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="119" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" ht="340" hidden="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
-        <v>753</v>
+        <v>482</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>10</v>
@@ -7744,32 +7747,35 @@
       <c r="D119" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G119" s="2" t="s">
-        <v>482</v>
+      <c r="E119" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>777</v>
       </c>
       <c r="I119" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J119" s="2" t="s">
-        <v>552</v>
+        <v>796</v>
       </c>
       <c r="K119" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L119" s="2" t="str">
         <f>A119</f>
-        <v>ModelConfigInterfaceMethods</v>
+        <v>ModelConfigInterface</v>
       </c>
       <c r="M119" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="N119" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="120" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
-        <v>199</v>
+        <v>749</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>10</v>
@@ -7778,22 +7784,23 @@
         <v>11</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>197</v>
+        <v>482</v>
       </c>
       <c r="I120" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J120" s="2" t="s">
-        <v>200</v>
+        <v>552</v>
       </c>
       <c r="K120" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="L120" s="2" t="s">
-        <v>199</v>
+      <c r="L120" s="2" t="str">
+        <f>A120</f>
+        <v>ModelConfigInterfaceMethods</v>
       </c>
       <c r="M120" s="2" t="s">
-        <v>922</v>
+        <v>764</v>
       </c>
       <c r="N120" s="2" t="s">
         <v>148</v>
@@ -7801,7 +7808,7 @@
     </row>
     <row r="121" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>10</v>
@@ -7816,16 +7823,16 @@
         <v>35</v>
       </c>
       <c r="J121" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="K121" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L121" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="M121" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N121" s="2" t="s">
         <v>148</v>
@@ -7833,7 +7840,7 @@
     </row>
     <row r="122" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>10</v>
@@ -7848,16 +7855,16 @@
         <v>35</v>
       </c>
       <c r="J122" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="K122" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L122" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="M122" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N122" s="2" t="s">
         <v>148</v>
@@ -7865,7 +7872,7 @@
     </row>
     <row r="123" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>10</v>
@@ -7880,16 +7887,16 @@
         <v>35</v>
       </c>
       <c r="J123" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="K123" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L123" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M123" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N123" s="2" t="s">
         <v>148</v>
@@ -7897,7 +7904,7 @@
     </row>
     <row r="124" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>10</v>
@@ -7912,16 +7919,16 @@
         <v>35</v>
       </c>
       <c r="J124" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="K124" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L124" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M124" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N124" s="2" t="s">
         <v>148</v>
@@ -7929,7 +7936,7 @@
     </row>
     <row r="125" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>10</v>
@@ -7950,10 +7957,10 @@
         <v>160</v>
       </c>
       <c r="L125" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="M125" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N125" s="2" t="s">
         <v>148</v>
@@ -7961,7 +7968,7 @@
     </row>
     <row r="126" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>10</v>
@@ -7969,20 +7976,23 @@
       <c r="D126" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="G126" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="I126" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J126" s="2" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="K126" s="2" t="s">
         <v>160</v>
       </c>
       <c r="L126" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M126" s="2" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="N126" s="2" t="s">
         <v>148</v>
@@ -7990,97 +8000,94 @@
     </row>
     <row r="127" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="L127" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>918</v>
+      </c>
+      <c r="N127" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="128" spans="1:14" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A128" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B128" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="C127" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="K127" s="2" t="s">
+      <c r="C128" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K128" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L127" s="2" t="s">
+      <c r="L128" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="M127" s="2" t="s">
-        <v>860</v>
-      </c>
-      <c r="N127" s="2" t="s">
+      <c r="M128" s="2" t="s">
+        <v>856</v>
+      </c>
+      <c r="N128" s="2" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="128" spans="1:14" ht="51" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="2" t="s">
+    <row r="129" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A129" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C128" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="K128" s="2" t="s">
+      <c r="C129" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="K129" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="L128" s="2" t="s">
+      <c r="L129" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="M128" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="N128" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="129" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="C129" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J129" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="L129" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="M129" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="N129" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S129" s="6">
-        <v>44025</v>
-      </c>
     </row>
     <row r="130" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>10</v>
@@ -8088,31 +8095,31 @@
       <c r="D130" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E130" s="2" t="s">
-        <v>248</v>
-      </c>
       <c r="I130" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J130" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K130" s="2" t="s">
         <v>185</v>
       </c>
       <c r="L130" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="M130" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="N130" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="S130" s="6">
+        <v>44025</v>
+      </c>
     </row>
     <row r="131" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
-        <v>783</v>
+        <v>214</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>10</v>
@@ -8121,40 +8128,30 @@
         <v>11</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>694</v>
+        <v>248</v>
       </c>
       <c r="I131" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J131" s="2" t="s">
-        <v>917</v>
+        <v>215</v>
       </c>
       <c r="K131" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="L131" s="2" t="str">
-        <f>A131</f>
-        <v>PermissionBean</v>
+        <v>185</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="M131" s="2" t="s">
-        <v>916</v>
+        <v>846</v>
       </c>
       <c r="N131" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="P131" s="6">
-        <v>44181</v>
-      </c>
-    </row>
-    <row r="132" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
-        <v>912</v>
+        <v>779</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>10</v>
@@ -8166,28 +8163,37 @@
         <v>112</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>786</v>
+        <v>908</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>694</v>
       </c>
       <c r="I132" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J132" s="2" t="s">
-        <v>169</v>
+        <v>913</v>
       </c>
       <c r="K132" s="2" t="s">
         <v>154</v>
       </c>
       <c r="L132" s="2" t="str">
         <f>A132</f>
-        <v>PermissionBeanInterface</v>
+        <v>PermissionBean</v>
       </c>
       <c r="M132" s="2" t="s">
-        <v>862</v>
+        <v>912</v>
+      </c>
+      <c r="N132" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="P132" s="6">
+        <v>44181</v>
       </c>
     </row>
     <row r="133" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
-        <v>784</v>
+        <v>908</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>10</v>
@@ -8199,34 +8205,28 @@
         <v>112</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>792</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>741</v>
+        <v>782</v>
       </c>
       <c r="I133" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J133" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K133" s="2" t="s">
         <v>154</v>
       </c>
       <c r="L133" s="2" t="str">
         <f>A133</f>
-        <v>PermissionConfig</v>
+        <v>PermissionBeanInterface</v>
       </c>
       <c r="M133" s="2" t="s">
-        <v>915</v>
-      </c>
-      <c r="P133" s="6">
-        <v>44181</v>
+        <v>858</v>
       </c>
     </row>
     <row r="134" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>10</v>
@@ -8237,32 +8237,35 @@
       <c r="E134" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="F134" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>737</v>
+      </c>
       <c r="I134" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J134" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K134" s="2" t="s">
         <v>154</v>
       </c>
       <c r="L134" s="2" t="str">
         <f>A134</f>
-        <v>PermissionConfigInterface</v>
+        <v>PermissionConfig</v>
       </c>
       <c r="M134" s="2" t="s">
-        <v>863</v>
+        <v>911</v>
       </c>
       <c r="P134" s="6">
         <v>44181</v>
       </c>
-      <c r="S134" s="6">
-        <v>44046</v>
-      </c>
-    </row>
-    <row r="135" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>10</v>
@@ -8270,8 +8273,8 @@
       <c r="D135" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F135" s="2" t="s">
-        <v>786</v>
+      <c r="E135" s="2" t="s">
+        <v>112</v>
       </c>
       <c r="I135" s="2" t="s">
         <v>35</v>
@@ -8284,21 +8287,21 @@
       </c>
       <c r="L135" s="2" t="str">
         <f>A135</f>
-        <v>PermissionConfigInterfaceMethods</v>
+        <v>PermissionConfigInterface</v>
       </c>
       <c r="M135" s="2" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="P135" s="6">
-        <v>44136</v>
+        <v>44181</v>
       </c>
       <c r="S135" s="6">
         <v>44046</v>
       </c>
     </row>
-    <row r="136" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
-        <v>545</v>
+        <v>788</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>10</v>
@@ -8306,73 +8309,74 @@
       <c r="D136" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E136" s="2" t="s">
-        <v>249</v>
+      <c r="F136" s="2" t="s">
+        <v>782</v>
       </c>
       <c r="I136" s="2" t="s">
         <v>35</v>
       </c>
       <c r="J136" s="2" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="K136" s="2" t="s">
         <v>154</v>
       </c>
       <c r="L136" s="2" t="str">
         <f>A136</f>
+        <v>PermissionConfigInterfaceMethods</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>859</v>
+      </c>
+      <c r="P136" s="6">
+        <v>44136</v>
+      </c>
+      <c r="S136" s="6">
+        <v>44046</v>
+      </c>
+    </row>
+    <row r="137" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="L137" s="2" t="str">
+        <f>A137</f>
         <v>PermissionRole</v>
       </c>
-      <c r="M136" s="2" t="s">
-        <v>864</v>
-      </c>
-      <c r="N136" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="S136" s="6">
-        <v>44069</v>
-      </c>
-    </row>
-    <row r="137" spans="1:19" ht="93" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="J137" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="L137" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="M137" s="2" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="N137" s="2" t="s">
         <v>148</v>
       </c>
       <c r="S137" s="6">
-        <v>44046</v>
-      </c>
-    </row>
-    <row r="138" spans="1:19" ht="125" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>44069</v>
+      </c>
+    </row>
+    <row r="138" spans="1:19" ht="93" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>10</v>
@@ -8383,28 +8387,31 @@
       <c r="I138" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="J138" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="K138" s="2" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="L138" s="2" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M138" s="2" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
       <c r="N138" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S138" s="6">
         <v>44046</v>
       </c>
     </row>
-    <row r="139" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:19" ht="125" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>10</v>
@@ -8415,20 +8422,17 @@
       <c r="I139" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J139" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="K139" s="2" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="L139" s="2" t="s">
-        <v>125</v>
+        <v>220</v>
       </c>
       <c r="M139" s="2" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="N139" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="S139" s="6">
         <v>44046</v>
@@ -8436,7 +8440,7 @@
     </row>
     <row r="140" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
-        <v>222</v>
+        <v>125</v>
       </c>
       <c r="B140" s="2" t="s">
         <v>207</v>
@@ -8450,25 +8454,31 @@
       <c r="I140" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="J140" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="K140" s="2" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="L140" s="2" t="s">
-        <v>222</v>
+        <v>125</v>
       </c>
       <c r="M140" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="N140" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S140" s="6">
         <v>44046</v>
       </c>
     </row>
-    <row r="141" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
-        <v>634</v>
+        <v>222</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>10</v>
@@ -8476,27 +8486,20 @@
       <c r="D141" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G141" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="I141" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="J141" s="2" t="s">
-        <v>635</v>
-      </c>
       <c r="K141" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="L141" s="2" t="str">
-        <f>A141</f>
-        <v>SimpleCommand</v>
+        <v>152</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>222</v>
       </c>
       <c r="M141" s="2" t="s">
-        <v>768</v>
+        <v>850</v>
       </c>
       <c r="N141" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="S141" s="6">
         <v>44046</v>
@@ -8504,7 +8507,7 @@
     </row>
     <row r="142" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
-        <v>223</v>
+        <v>634</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>10</v>
@@ -8512,41 +8515,35 @@
       <c r="D142" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F142" s="2" t="s">
-        <v>634</v>
-      </c>
       <c r="G142" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="I142" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J142" s="2" t="s">
-        <v>224</v>
+        <v>635</v>
       </c>
       <c r="K142" s="2" t="s">
-        <v>184</v>
+        <v>614</v>
       </c>
       <c r="L142" s="2" t="str">
         <f>A142</f>
-        <v>SinusValueCall</v>
+        <v>SimpleCommand</v>
       </c>
       <c r="M142" s="2" t="s">
-        <v>864</v>
+        <v>764</v>
       </c>
       <c r="N142" s="2" t="s">
         <v>148</v>
       </c>
       <c r="S142" s="6">
-        <v>43390</v>
+        <v>44046</v>
       </c>
     </row>
     <row r="143" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
-        <v>662</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>10</v>
@@ -8554,38 +8551,44 @@
       <c r="D143" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="F143" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="I143" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J143" s="2" t="s">
-        <v>664</v>
+        <v>224</v>
       </c>
       <c r="K143" s="2" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="L143" s="2" t="str">
         <f>A143</f>
-        <v>SortOrder</v>
+        <v>SinusValueCall</v>
       </c>
       <c r="M143" s="2" t="s">
-        <v>855</v>
+        <v>860</v>
       </c>
       <c r="N143" s="2" t="s">
         <v>148</v>
       </c>
       <c r="S143" s="6">
-        <v>44123</v>
-      </c>
-    </row>
-    <row r="144" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
+        <v>43390</v>
+      </c>
+    </row>
+    <row r="144" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
-        <v>13</v>
+        <v>662</v>
       </c>
       <c r="B144" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>333</v>
+        <v>10</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>11</v>
@@ -8593,28 +8596,35 @@
       <c r="I144" s="2" t="s">
         <v>35</v>
       </c>
+      <c r="J144" s="2" t="s">
+        <v>664</v>
+      </c>
       <c r="K144" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="L144" s="2" t="s">
-        <v>13</v>
+        <v>163</v>
+      </c>
+      <c r="L144" s="2" t="str">
+        <f>A144</f>
+        <v>SortOrder</v>
       </c>
       <c r="M144" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
+      </c>
+      <c r="N144" s="2" t="s">
+        <v>148</v>
       </c>
       <c r="S144" s="6">
-        <v>44041</v>
+        <v>44123</v>
       </c>
     </row>
     <row r="145" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
-        <v>225</v>
+        <v>13</v>
       </c>
       <c r="B145" s="2" t="s">
         <v>207</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>10</v>
+        <v>333</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>11</v>
@@ -8625,23 +8635,19 @@
       <c r="K145" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="L145" s="2" t="str">
-        <f>A145</f>
-        <v>StringBuffer</v>
+      <c r="L145" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="M145" s="2" t="s">
-        <v>854</v>
-      </c>
-      <c r="N145" s="2" t="s">
-        <v>151</v>
+        <v>849</v>
       </c>
       <c r="S145" s="6">
-        <v>44100</v>
+        <v>44041</v>
       </c>
     </row>
     <row r="146" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B146" s="2" t="s">
         <v>207</v>
@@ -8660,21 +8666,24 @@
       </c>
       <c r="L146" s="2" t="str">
         <f>A146</f>
-        <v>StringBuilder</v>
+        <v>StringBuffer</v>
       </c>
       <c r="M146" s="2" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="N146" s="2" t="s">
         <v>151</v>
       </c>
       <c r="S146" s="6">
-        <v>44070</v>
-      </c>
-    </row>
-    <row r="147" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+        <v>44100</v>
+      </c>
+    </row>
+    <row r="147" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>207</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>10</v>
@@ -8682,35 +8691,29 @@
       <c r="D147" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F147" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="G147" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="I147" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>228</v>
+        <v>35</v>
       </c>
       <c r="K147" s="2" t="s">
-        <v>184</v>
+        <v>152</v>
       </c>
       <c r="L147" s="2" t="str">
         <f>A147</f>
-        <v>StringLowerCall</v>
+        <v>StringBuilder</v>
       </c>
       <c r="M147" s="2" t="s">
-        <v>864</v>
+        <v>850</v>
       </c>
       <c r="N147" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="148" spans="1:19" ht="118" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+      <c r="S147" s="6">
+        <v>44070</v>
+      </c>
+    </row>
+    <row r="148" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
-        <v>735</v>
+        <v>227</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>10</v>
@@ -8735,21 +8738,18 @@
       </c>
       <c r="L148" s="2" t="str">
         <f>A148</f>
-        <v>StringLowerFirstCharCall</v>
+        <v>StringLowerCall</v>
       </c>
       <c r="M148" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N148" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S148" s="6">
-        <v>44046</v>
-      </c>
-    </row>
-    <row r="149" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:19" ht="118" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>10</v>
@@ -8774,18 +8774,21 @@
       </c>
       <c r="L149" s="2" t="str">
         <f>A149</f>
-        <v>StringPluralCall</v>
+        <v>StringLowerFirstCharCall</v>
       </c>
       <c r="M149" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N149" s="2" t="s">
         <v>148</v>
       </c>
+      <c r="S149" s="6">
+        <v>44046</v>
+      </c>
     </row>
     <row r="150" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
-        <v>229</v>
+        <v>730</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>10</v>
@@ -8793,11 +8796,8 @@
       <c r="D150" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E150" s="2" t="s">
-        <v>733</v>
-      </c>
       <c r="F150" s="2" t="s">
-        <v>534</v>
+        <v>634</v>
       </c>
       <c r="G150" s="2" t="s">
         <v>156</v>
@@ -8806,17 +8806,17 @@
         <v>14</v>
       </c>
       <c r="J150" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="K150" s="2" t="s">
         <v>184</v>
       </c>
       <c r="L150" s="2" t="str">
         <f>A150</f>
-        <v>StringReplaceCall</v>
+        <v>StringPluralCall</v>
       </c>
       <c r="M150" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N150" s="2" t="s">
         <v>148</v>
@@ -8824,7 +8824,7 @@
     </row>
     <row r="151" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
-        <v>409</v>
+        <v>229</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>10</v>
@@ -8832,8 +8832,11 @@
       <c r="D151" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E151" s="2" t="s">
+        <v>729</v>
+      </c>
       <c r="F151" s="2" t="s">
-        <v>634</v>
+        <v>534</v>
       </c>
       <c r="G151" s="2" t="s">
         <v>156</v>
@@ -8842,28 +8845,25 @@
         <v>14</v>
       </c>
       <c r="J151" s="2" t="s">
-        <v>408</v>
+        <v>230</v>
       </c>
       <c r="K151" s="2" t="s">
         <v>184</v>
       </c>
       <c r="L151" s="2" t="str">
         <f>A151</f>
-        <v>StringReplaceWhiteSpaceCall</v>
+        <v>StringReplaceCall</v>
       </c>
       <c r="M151" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N151" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S151" s="6">
-        <v>44060</v>
-      </c>
     </row>
     <row r="152" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>10</v>
@@ -8888,19 +8888,21 @@
       </c>
       <c r="L152" s="2" t="str">
         <f>A152</f>
-        <v>StringReplaceWithHtmlCall</v>
+        <v>StringReplaceWhiteSpaceCall</v>
       </c>
       <c r="M152" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N152" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S152" s="7"/>
+      <c r="S152" s="6">
+        <v>44060</v>
+      </c>
     </row>
     <row r="153" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
-        <v>231</v>
+        <v>415</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>10</v>
@@ -8918,17 +8920,17 @@
         <v>14</v>
       </c>
       <c r="J153" s="2" t="s">
-        <v>232</v>
+        <v>408</v>
       </c>
       <c r="K153" s="2" t="s">
         <v>184</v>
       </c>
       <c r="L153" s="2" t="str">
         <f>A153</f>
-        <v>StringUpperCall</v>
+        <v>StringReplaceWithHtmlCall</v>
       </c>
       <c r="M153" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N153" s="2" t="s">
         <v>148</v>
@@ -8937,7 +8939,7 @@
     </row>
     <row r="154" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>10</v>
@@ -8962,10 +8964,10 @@
       </c>
       <c r="L154" s="2" t="str">
         <f>A154</f>
-        <v>StringUpperFirstCharCall</v>
+        <v>StringUpperCall</v>
       </c>
       <c r="M154" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N154" s="2" t="s">
         <v>148</v>
@@ -8974,7 +8976,7 @@
     </row>
     <row r="155" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>10</v>
@@ -8982,11 +8984,8 @@
       <c r="D155" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E155" s="2" t="s">
-        <v>793</v>
-      </c>
       <c r="F155" s="2" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>156</v>
@@ -8995,26 +8994,26 @@
         <v>14</v>
       </c>
       <c r="J155" s="2" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="K155" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="L155" s="2" t="str">
         <f>A155</f>
-        <v>TemplateCall</v>
+        <v>StringUpperFirstCharCall</v>
       </c>
       <c r="M155" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N155" s="2" t="s">
         <v>148</v>
       </c>
       <c r="S155" s="7"/>
     </row>
-    <row r="156" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2" t="s">
-        <v>528</v>
+        <v>234</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>10</v>
@@ -9022,35 +9021,39 @@
       <c r="D156" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E156" s="2" t="s">
+        <v>789</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>637</v>
+      </c>
       <c r="G156" s="2" t="s">
-        <v>459</v>
+        <v>156</v>
       </c>
       <c r="I156" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J156" s="2" t="s">
-        <v>594</v>
+        <v>235</v>
       </c>
       <c r="K156" s="2" t="s">
         <v>186</v>
       </c>
       <c r="L156" s="2" t="str">
         <f>A156</f>
-        <v>TemplateDirResourceCall</v>
+        <v>TemplateCall</v>
       </c>
       <c r="M156" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N156" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S156" s="7">
-        <v>44141</v>
-      </c>
-    </row>
-    <row r="157" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="S156" s="7"/>
+    </row>
+    <row r="157" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2" t="s">
-        <v>236</v>
+        <v>528</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>10</v>
@@ -9059,23 +9062,23 @@
         <v>11</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>180</v>
+        <v>459</v>
       </c>
       <c r="I157" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J157" s="2" t="s">
-        <v>529</v>
+        <v>594</v>
       </c>
       <c r="K157" s="2" t="s">
         <v>186</v>
       </c>
       <c r="L157" s="2" t="str">
         <f>A157</f>
-        <v>TemplateResourceCall</v>
+        <v>TemplateDirResourceCall</v>
       </c>
       <c r="M157" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N157" s="2" t="s">
         <v>148</v>
@@ -9086,7 +9089,7 @@
     </row>
     <row r="158" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2" t="s">
-        <v>399</v>
+        <v>236</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>10</v>
@@ -9095,107 +9098,113 @@
         <v>11</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>621</v>
+        <v>180</v>
       </c>
       <c r="I158" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J158" s="2" t="s">
-        <v>590</v>
+        <v>529</v>
       </c>
       <c r="K158" s="2" t="s">
         <v>186</v>
       </c>
       <c r="L158" s="2" t="str">
         <f>A158</f>
-        <v>TemplateResourceStoreCall</v>
+        <v>TemplateResourceCall</v>
       </c>
       <c r="M158" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N158" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S158" s="7"/>
+      <c r="S158" s="7">
+        <v>44141</v>
+      </c>
     </row>
     <row r="159" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2" t="s">
-        <v>250</v>
+        <v>399</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>251</v>
+        <v>10</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E159" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>634</v>
-      </c>
       <c r="G159" s="2" t="s">
-        <v>156</v>
+        <v>621</v>
       </c>
       <c r="I159" s="2" t="s">
         <v>14</v>
       </c>
       <c r="J159" s="2" t="s">
-        <v>252</v>
+        <v>590</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="L159" s="2" t="str">
         <f>A159</f>
-        <v>TheGreetingCall</v>
+        <v>TemplateResourceStoreCall</v>
       </c>
       <c r="M159" s="2" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="N159" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S159" s="7">
-        <v>44141</v>
-      </c>
-    </row>
-    <row r="160" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
+      <c r="S159" s="7"/>
+    </row>
+    <row r="160" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>10</v>
+        <v>251</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E160" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="I160" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>252</v>
       </c>
       <c r="K160" s="2" t="s">
-        <v>149</v>
+        <v>184</v>
       </c>
       <c r="L160" s="2" t="str">
         <f>A160</f>
-        <v>TreeMap</v>
+        <v>TheGreetingCall</v>
       </c>
       <c r="M160" s="2" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="N160" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="S160" s="7">
         <v>44141</v>
       </c>
     </row>
-    <row r="161" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2" t="s">
-        <v>237</v>
+        <v>581</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>201</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>10</v>
@@ -9203,75 +9212,70 @@
       <c r="D161" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E161" s="2" t="s">
-        <v>639</v>
-      </c>
-      <c r="F161" s="2" t="s">
-        <v>637</v>
-      </c>
-      <c r="G161" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="I161" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="J161" s="2" t="s">
-        <v>238</v>
+        <v>35</v>
       </c>
       <c r="K161" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="L161" s="2" t="s">
-        <v>237</v>
+        <v>149</v>
+      </c>
+      <c r="L161" s="2" t="str">
+        <f>A161</f>
+        <v>TreeMap</v>
       </c>
       <c r="M161" s="2" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
       <c r="N161" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="S161" s="7">
         <v>44141</v>
       </c>
     </row>
-    <row r="162" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>361</v>
+        <v>10</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E162" s="2" t="s">
+        <v>639</v>
+      </c>
       <c r="F162" s="2" t="s">
-        <v>817</v>
+        <v>637</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>178</v>
+        <v>156</v>
       </c>
       <c r="I162" s="2" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="J162" s="2" t="s">
-        <v>254</v>
+        <v>238</v>
       </c>
       <c r="K162" s="2" t="s">
-        <v>255</v>
+        <v>184</v>
       </c>
       <c r="L162" s="2" t="s">
-        <v>253</v>
+        <v>237</v>
       </c>
       <c r="M162" s="2" t="s">
-        <v>922</v>
+        <v>860</v>
       </c>
       <c r="N162" s="2" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="163" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
+      <c r="S162" s="7">
+        <v>44141</v>
+      </c>
+    </row>
+    <row r="163" spans="1:19" ht="34" hidden="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2" t="s">
-        <v>817</v>
+        <v>253</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>361</v>
@@ -9279,11 +9283,11 @@
       <c r="D163" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E163" s="2" t="s">
-        <v>818</v>
-      </c>
       <c r="F163" s="2" t="s">
-        <v>785</v>
+        <v>813</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>178</v>
       </c>
       <c r="I163" s="2" t="s">
         <v>35</v>
@@ -9292,22 +9296,21 @@
         <v>254</v>
       </c>
       <c r="K163" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="L163" s="2" t="str">
-        <f>A163</f>
-        <v>XlsxConfigInterface</v>
+        <v>179</v>
+      </c>
+      <c r="L163" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="M163" s="2" t="s">
-        <v>768</v>
+        <v>918</v>
       </c>
       <c r="N163" s="2" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="164" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:19" ht="68" hidden="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2" t="s">
-        <v>256</v>
+        <v>813</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>361</v>
@@ -9315,53 +9318,83 @@
       <c r="D164" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="E164" s="2" t="s">
+        <v>814</v>
+      </c>
       <c r="F164" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>180</v>
+        <v>781</v>
       </c>
       <c r="I164" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="J164" s="2" t="s">
-        <v>677</v>
+        <v>254</v>
       </c>
       <c r="K164" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="L164" s="2" t="s">
-        <v>256</v>
+        <v>179</v>
+      </c>
+      <c r="L164" s="2" t="str">
+        <f>A164</f>
+        <v>XlsxConfigInterface</v>
       </c>
       <c r="M164" s="2" t="s">
-        <v>864</v>
+        <v>764</v>
       </c>
       <c r="N164" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="S164" s="7">
+    </row>
+    <row r="165" spans="1:19" ht="51" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>860</v>
+      </c>
+      <c r="N165" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="S165" s="7">
         <v>44141</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N164" xr:uid="{A955F0F7-5ED5-4A4E-94AE-7EA930688524}">
+  <autoFilter ref="A1:N165" xr:uid="{A955F0F7-5ED5-4A4E-94AE-7EA930688524}">
     <filterColumn colId="2">
       <filters>
-        <filter val="elastic-objects"/>
-        <filter val="eo-csv"/>
+        <filter val="builder"/>
       </filters>
     </filterColumn>
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter val="*CsvConfig*"/>
-      </customFilters>
-    </filterColumn>
-    <sortState ref="A2:N151">
-      <sortCondition ref="A2:A151"/>
+    <sortState ref="A2:N152">
+      <sortCondition ref="A2:A152"/>
     </sortState>
   </autoFilter>
-  <sortState ref="A2:P164">
-    <sortCondition ref="A2:A164"/>
+  <sortState ref="A2:P165">
+    <sortCondition ref="A2:A165"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -9430,7 +9463,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="F2" t="s">
         <v>35</v>
@@ -9441,12 +9474,12 @@
         <v>absolute</v>
       </c>
       <c r="J2" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="100" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B3" t="s">
         <v>10</v>
@@ -9458,7 +9491,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F3" t="s">
         <v>35</v>
@@ -9469,12 +9502,12 @@
         <v>abstract</v>
       </c>
       <c r="J3" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="100" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B4" t="s">
         <v>10</v>
@@ -9486,7 +9519,7 @@
         <v>16</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="F4" t="s">
         <v>35</v>
@@ -9497,7 +9530,7 @@
         <v>abstract</v>
       </c>
       <c r="J4" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="100" customHeight="1" x14ac:dyDescent="0.2">
@@ -9514,7 +9547,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
@@ -9529,7 +9562,7 @@
     </row>
     <row r="6" spans="1:10" ht="100" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="B6" t="s">
         <v>10</v>
@@ -9541,7 +9574,7 @@
         <v>13</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="F6" t="s">
         <v>35</v>
@@ -9555,7 +9588,7 @@
         <v>32</v>
       </c>
       <c r="J6" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="100" customHeight="1" x14ac:dyDescent="0.2">
@@ -9593,7 +9626,7 @@
         <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>19</v>
@@ -9620,7 +9653,7 @@
         <v>16</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="F9" t="s">
         <v>35</v>
@@ -9852,7 +9885,7 @@
     </row>
     <row r="18" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B18" t="s">
         <v>10</v>
@@ -9864,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="F18" t="s">
         <v>35</v>
@@ -9875,12 +9908,12 @@
         <v>dbAnnotated</v>
       </c>
       <c r="J18" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B19" t="s">
         <v>10</v>
@@ -9892,7 +9925,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F19" t="s">
         <v>35</v>
@@ -9903,7 +9936,7 @@
         <v>dbAnnotated</v>
       </c>
       <c r="J19" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -9986,7 +10019,7 @@
     </row>
     <row r="23" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B23" t="s">
         <v>10</v>
@@ -9998,7 +10031,7 @@
         <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="F23" t="s">
         <v>35</v>
@@ -10009,7 +10042,7 @@
         <v>default</v>
       </c>
       <c r="J23" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -10332,7 +10365,7 @@
     </row>
     <row r="36" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B36" t="s">
         <v>10</v>
@@ -10341,10 +10374,10 @@
         <v>11</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="F36" t="s">
         <v>35</v>
@@ -10382,7 +10415,7 @@
         <v>4</v>
       </c>
       <c r="J37" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="38" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -10424,7 +10457,7 @@
         <v>11</v>
       </c>
       <c r="D39" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E39" s="1" t="s">
         <v>50</v>
@@ -10464,7 +10497,7 @@
         <v>80</v>
       </c>
       <c r="J40" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -10606,7 +10639,7 @@
     </row>
     <row r="46" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B46" t="s">
         <v>10</v>
@@ -10618,7 +10651,7 @@
         <v>16</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="F46" t="s">
         <v>35</v>
@@ -10629,12 +10662,12 @@
         <v>final</v>
       </c>
       <c r="J46" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B47" t="s">
         <v>10</v>
@@ -10646,7 +10679,7 @@
         <v>16</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="F47" t="s">
         <v>35</v>
@@ -10657,7 +10690,7 @@
         <v>generated</v>
       </c>
       <c r="J47" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -10794,7 +10827,7 @@
         <v>80</v>
       </c>
       <c r="J52" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -10811,7 +10844,7 @@
         <v>39</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
@@ -10932,7 +10965,7 @@
     </row>
     <row r="58" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B58" t="s">
         <v>301</v>
@@ -10944,7 +10977,7 @@
         <v>13</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="F58" t="s">
         <v>35</v>
@@ -10958,12 +10991,12 @@
         <v>10000</v>
       </c>
       <c r="J58" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B59" t="s">
         <v>301</v>
@@ -10975,7 +11008,7 @@
         <v>13</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="F59" t="s">
         <v>35</v>
@@ -10989,12 +11022,12 @@
         <v>1028</v>
       </c>
       <c r="J59" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="B60" t="s">
         <v>301</v>
@@ -11006,7 +11039,7 @@
         <v>13</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F60" t="s">
         <v>35</v>
@@ -11020,12 +11053,12 @@
         <v>512</v>
       </c>
       <c r="J60" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="B61" t="s">
         <v>301</v>
@@ -11037,7 +11070,7 @@
         <v>13</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F61" t="s">
         <v>35</v>
@@ -11051,12 +11084,12 @@
         <v>128</v>
       </c>
       <c r="J61" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="B62" t="s">
         <v>301</v>
@@ -11068,7 +11101,7 @@
         <v>13</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F62" t="s">
         <v>35</v>
@@ -11082,12 +11115,12 @@
         <v>512</v>
       </c>
       <c r="J62" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="B63" t="s">
         <v>301</v>
@@ -11099,7 +11132,7 @@
         <v>13</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="F63" t="s">
         <v>35</v>
@@ -11113,12 +11146,12 @@
         <v>512</v>
       </c>
       <c r="J63" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="B64" t="s">
         <v>301</v>
@@ -11130,7 +11163,7 @@
         <v>13</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="F64" t="s">
         <v>35</v>
@@ -11144,12 +11177,12 @@
         <v>512</v>
       </c>
       <c r="J64" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="B65" t="s">
         <v>301</v>
@@ -11161,7 +11194,7 @@
         <v>13</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="F65" t="s">
         <v>35</v>
@@ -11175,12 +11208,12 @@
         <v>1028</v>
       </c>
       <c r="J65" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="B66" t="s">
         <v>301</v>
@@ -11192,7 +11225,7 @@
         <v>13</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="F66" t="s">
         <v>35</v>
@@ -11206,12 +11239,12 @@
         <v>512</v>
       </c>
       <c r="J66" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
       <c r="B67" t="s">
         <v>301</v>
@@ -11223,7 +11256,7 @@
         <v>13</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="F67" t="s">
         <v>35</v>
@@ -11237,12 +11270,12 @@
         <v>512</v>
       </c>
       <c r="J67" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="B68" t="s">
         <v>301</v>
@@ -11254,7 +11287,7 @@
         <v>13</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="F68" t="s">
         <v>35</v>
@@ -11268,7 +11301,7 @@
         <v>1028</v>
       </c>
       <c r="J68" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.2">
@@ -11309,7 +11342,7 @@
         <v>13</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="F70" t="s">
         <v>35</v>
@@ -11323,7 +11356,7 @@
         <v>10</v>
       </c>
       <c r="J70" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -11354,12 +11387,12 @@
         <v>64</v>
       </c>
       <c r="J71" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B72" t="s">
         <v>301</v>
@@ -11371,7 +11404,7 @@
         <v>13</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="F72" t="s">
         <v>35</v>
@@ -11385,12 +11418,12 @@
         <v>512</v>
       </c>
       <c r="J72" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="B73" t="s">
         <v>301</v>
@@ -11402,7 +11435,7 @@
         <v>13</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="F73" t="s">
         <v>35</v>
@@ -11416,7 +11449,7 @@
         <v>1028</v>
       </c>
       <c r="J73" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -11504,7 +11537,7 @@
     </row>
     <row r="77" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
       <c r="B77" t="s">
         <v>10</v>
@@ -11528,7 +11561,7 @@
         <v>jsonIgnore</v>
       </c>
       <c r="J77" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -11717,7 +11750,7 @@
     </row>
     <row r="85" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="B85" t="s">
         <v>10</v>
@@ -11729,7 +11762,7 @@
         <v>67</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="F85" t="s">
         <v>35</v>
@@ -11740,12 +11773,12 @@
         <v>max</v>
       </c>
       <c r="J85" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="86" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
       <c r="B86" t="s">
         <v>10</v>
@@ -11757,7 +11790,7 @@
         <v>67</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
       <c r="F86" t="s">
         <v>35</v>
@@ -11768,7 +11801,7 @@
         <v>min</v>
       </c>
       <c r="J86" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -11854,7 +11887,7 @@
         <v>64</v>
       </c>
       <c r="J89" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="90" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -11885,7 +11918,7 @@
         <v>64</v>
       </c>
       <c r="J90" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="91" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -11916,7 +11949,7 @@
         <v>64</v>
       </c>
       <c r="J91" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -11999,7 +12032,7 @@
     </row>
     <row r="95" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B95" t="s">
         <v>10</v>
@@ -12011,7 +12044,7 @@
         <v>30</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
@@ -12138,7 +12171,7 @@
         <v>11</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>643</v>
@@ -12163,7 +12196,7 @@
         <v>11</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>644</v>
@@ -12569,12 +12602,12 @@
         <v>98</v>
       </c>
       <c r="J116" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="117" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B117" t="s">
         <v>10</v>
@@ -12586,7 +12619,7 @@
         <v>16</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="F117" t="s">
         <v>35</v>
@@ -12597,7 +12630,7 @@
         <v>override</v>
       </c>
       <c r="J117" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="118" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -12614,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="F118" t="s">
         <v>14</v>
@@ -12625,7 +12658,7 @@
         <v>overwrite</v>
       </c>
       <c r="J118" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="119" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -12710,7 +12743,7 @@
         <v>15</v>
       </c>
       <c r="J121" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="122" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -12766,7 +12799,7 @@
         <v>port</v>
       </c>
       <c r="J123" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="124" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -12827,7 +12860,7 @@
     </row>
     <row r="126" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B126" t="s">
         <v>301</v>
@@ -12839,7 +12872,7 @@
         <v>13</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="F126" t="s">
         <v>35</v>
@@ -12879,7 +12912,7 @@
     </row>
     <row r="128" spans="1:10" ht="51" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="B128" t="s">
         <v>10</v>
@@ -12891,7 +12924,7 @@
         <v>16</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="F128" t="s">
         <v>35</v>
@@ -12902,7 +12935,7 @@
         <v>property</v>
       </c>
       <c r="J128" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="129" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -12933,7 +12966,7 @@
         <v>8</v>
       </c>
       <c r="J129" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="130" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -13043,7 +13076,7 @@
         <v>4</v>
       </c>
       <c r="J133" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="134" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13071,7 +13104,7 @@
         <v>115</v>
       </c>
       <c r="J134" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="135" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13099,7 +13132,7 @@
         <v>116</v>
       </c>
       <c r="J135" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="136" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13127,7 +13160,7 @@
         <v>117</v>
       </c>
       <c r="J136" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="137" spans="1:10" ht="34" x14ac:dyDescent="0.2">
@@ -13157,7 +13190,7 @@
         <v>80</v>
       </c>
       <c r="J137" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="138" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13171,7 +13204,7 @@
         <v>11</v>
       </c>
       <c r="D138" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>118</v>
@@ -13263,7 +13296,7 @@
         <v>shapeType</v>
       </c>
       <c r="J141" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="142" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13412,7 +13445,7 @@
         <v>11</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>647</v>
@@ -13482,7 +13515,7 @@
     </row>
     <row r="150" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="B150" t="s">
         <v>10</v>
@@ -13506,12 +13539,12 @@
         <v>staticName</v>
       </c>
       <c r="J150" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="151" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B151" t="s">
         <v>10</v>
@@ -13523,7 +13556,7 @@
         <v>16</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="F151" t="s">
         <v>35</v>
@@ -13534,7 +13567,7 @@
         <v>super</v>
       </c>
       <c r="J151" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="152" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13733,7 +13766,7 @@
     </row>
     <row r="159" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>10</v>
@@ -13745,7 +13778,7 @@
         <v>13</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="F159" t="s">
         <v>14</v>
@@ -13818,7 +13851,7 @@
     </row>
     <row r="162" spans="1:10" ht="34" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B162" t="s">
         <v>10</v>
@@ -13830,7 +13863,7 @@
         <v>16</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F162" t="s">
         <v>35</v>
@@ -13841,7 +13874,7 @@
         <v>transient</v>
       </c>
       <c r="J162" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
     </row>
     <row r="163" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13870,7 +13903,7 @@
         <v>unique</v>
       </c>
       <c r="J163" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="164" spans="1:10" x14ac:dyDescent="0.2">
@@ -13901,7 +13934,7 @@
     </row>
     <row r="165" spans="1:10" ht="17" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
       <c r="B165" t="s">
         <v>10</v>
@@ -13928,7 +13961,7 @@
         <v>80</v>
       </c>
       <c r="J165" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="166" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -13959,7 +13992,7 @@
         <v>50</v>
       </c>
       <c r="J166" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="167" spans="1:10" ht="17" x14ac:dyDescent="0.2">
@@ -14915,7 +14948,7 @@
     </row>
     <row r="8" spans="1:14" ht="102" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>680</v>
@@ -14946,12 +14979,12 @@
         <v>584</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>680</v>
@@ -14970,7 +15003,7 @@
         <v>=&gt;[shapeType].create.tpl</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>14</v>
@@ -15645,7 +15678,7 @@
         <v>eo.xlsx</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>14</v>
@@ -16059,7 +16092,7 @@
     </row>
     <row r="43" spans="1:14" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>301</v>
@@ -16264,7 +16297,7 @@
     </row>
     <row r="49" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>301</v>
@@ -16361,7 +16394,7 @@
     </row>
     <row r="52" spans="1:14" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>680</v>
@@ -16380,7 +16413,7 @@
         <v>ParamsEoConfigs.json</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>14</v>
@@ -16394,7 +16427,7 @@
     </row>
     <row r="53" spans="1:14" ht="85" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>680</v>
@@ -16413,7 +16446,7 @@
         <v>ParamsJava.json</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>14</v>
@@ -16866,10 +16899,10 @@
         <v>272</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>488</v>
